--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 DEER BUCK GENERAL SEASON MUZZLELOADER.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 DEER BUCK GENERAL SEASON MUZZLELOADER.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -577,10 +577,15 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Average Age Harvested (previous hunting season)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
@@ -645,7 +650,8 @@
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -710,7 +716,8 @@
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -775,7 +782,8 @@
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -840,7 +848,8 @@
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -905,7 +914,8 @@
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -970,7 +980,8 @@
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -1035,7 +1046,8 @@
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -1100,7 +1112,8 @@
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -1165,7 +1178,8 @@
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -1230,7 +1244,8 @@
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>4.6</t>
         </is>
@@ -1295,7 +1310,8 @@
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -1360,7 +1376,8 @@
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -1425,7 +1442,8 @@
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -1490,7 +1508,8 @@
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr"/>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1555,7 +1574,8 @@
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1620,7 +1640,8 @@
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>3.9</t>
         </is>
@@ -1685,7 +1706,8 @@
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -1750,7 +1772,8 @@
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
@@ -1815,7 +1838,8 @@
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -1880,7 +1904,8 @@
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1945,7 +1970,8 @@
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -2010,7 +2036,8 @@
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr"/>
-      <c r="O23" s="3" t="inlineStr">
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -2075,7 +2102,8 @@
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr"/>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -2140,7 +2168,8 @@
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr"/>
-      <c r="O25" s="3" t="inlineStr">
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr">
         <is>
           <t>4.8</t>
         </is>
@@ -2205,7 +2234,8 @@
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr"/>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -2270,7 +2300,8 @@
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr"/>
-      <c r="O27" s="3" t="inlineStr">
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -2335,7 +2366,8 @@
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -2400,7 +2432,8 @@
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr"/>
-      <c r="O29" s="3" t="inlineStr">
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
